--- a/artfynd/A 62748-2025 artfynd.xlsx
+++ b/artfynd/A 62748-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131251056</v>
+        <v>131246473</v>
       </c>
       <c r="B2" t="n">
-        <v>79264</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,40 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster om Lillberget, Dlr</t>
+          <t>Våtdalen, Våtdalen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476453</v>
+        <v>476394</v>
       </c>
       <c r="R2" t="n">
-        <v>6791813</v>
+        <v>6791767</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,62 +743,76 @@
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sparsamt på gran</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Peter Turander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131251025</v>
+        <v>131250853</v>
       </c>
       <c r="B3" t="n">
-        <v>79022</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -814,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476384</v>
+        <v>476587</v>
       </c>
       <c r="R3" t="n">
-        <v>6791757</v>
+        <v>6791621</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,14 +888,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131250994</v>
+        <v>131250866</v>
       </c>
       <c r="B4" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -915,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476315</v>
+        <v>476542</v>
       </c>
       <c r="R4" t="n">
-        <v>6791707</v>
+        <v>6791619</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,14 +989,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131250932</v>
+        <v>131250897</v>
       </c>
       <c r="B5" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1016,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476403</v>
+        <v>476512</v>
       </c>
       <c r="R5" t="n">
-        <v>6791632</v>
+        <v>6791624</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,14 +1090,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131251006</v>
+        <v>131250911</v>
       </c>
       <c r="B6" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1117,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476352</v>
+        <v>476459</v>
       </c>
       <c r="R6" t="n">
-        <v>6791734</v>
+        <v>6791628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-02-21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikliga förekomster. Garnlav på nästan varje tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,43 +1191,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131251168</v>
+        <v>131250920</v>
       </c>
       <c r="B7" t="n">
-        <v>5178</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476457</v>
+        <v>476423</v>
       </c>
       <c r="R7" t="n">
-        <v>6791813</v>
+        <v>6791627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,14 +1292,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131251036</v>
+        <v>131250932</v>
       </c>
       <c r="B8" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476381</v>
+        <v>476403</v>
       </c>
       <c r="R8" t="n">
-        <v>6791812</v>
+        <v>6791632</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,42 +1393,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131251145</v>
+        <v>131250975</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1436,10 +1431,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476457</v>
+        <v>476322</v>
       </c>
       <c r="R9" t="n">
-        <v>6791813</v>
+        <v>6791634</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1475,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,50 +1487,44 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131251048</v>
+        <v>131250985</v>
       </c>
       <c r="B10" t="n">
-        <v>8454</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1542,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476421</v>
+        <v>476312</v>
       </c>
       <c r="R10" t="n">
-        <v>6791782</v>
+        <v>6791663</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,39 +1588,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131251035</v>
+        <v>131250994</v>
       </c>
       <c r="B11" t="n">
-        <v>79022</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476381</v>
+        <v>476315</v>
       </c>
       <c r="R11" t="n">
-        <v>6791812</v>
+        <v>6791707</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,55 +1689,58 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131246473</v>
+        <v>131251006</v>
       </c>
       <c r="B12" t="n">
-        <v>79296</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Våtdalen, Våtdalen, Dlr</t>
+          <t>Öster om Lillberget, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>476394</v>
+        <v>476352</v>
       </c>
       <c r="R12" t="n">
-        <v>6791767</v>
+        <v>6791734</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1774,24 +1767,14 @@
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Sparsamt på gran</t>
+          <t>Rikliga förekomster. Garnlav på nästan varje tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,32 +1783,33 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Peter Turander</t>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131250985</v>
+        <v>131251036</v>
       </c>
       <c r="B13" t="n">
-        <v>79264</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1856,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>476312</v>
+        <v>476381</v>
       </c>
       <c r="R13" t="n">
-        <v>6791663</v>
+        <v>6791812</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,49 +1896,44 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131251185</v>
+        <v>131251056</v>
       </c>
       <c r="B14" t="n">
-        <v>57902</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1962,10 +1941,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>476452</v>
+        <v>476453</v>
       </c>
       <c r="R14" t="n">
-        <v>6791855</v>
+        <v>6791813</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,6 +1985,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2017,10 +1997,1266 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131251211</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>476552</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6791886</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
           <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131251145</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>476457</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6791813</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131251185</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>476452</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6791855</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131251168</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>476457</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6791813</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131250875</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>476518</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6791626</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131250883</v>
+      </c>
+      <c r="B20" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>476511</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6791623</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131250961</v>
+      </c>
+      <c r="B21" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>476402</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6791631</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131251048</v>
+      </c>
+      <c r="B22" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>476421</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6791782</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131251203</v>
+      </c>
+      <c r="B23" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>476552</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6791886</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131251025</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>476384</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6791757</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131251035</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>476381</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6791812</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Birgitta Kvist, Peter Turander, Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131251201</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Öster om Lillberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>476552</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6791886</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Peter Turander, Birgitta Kvist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62748-2025 artfynd.xlsx
+++ b/artfynd/A 62748-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131246473</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250853</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -986,6 +1001,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250866</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1087,6 +1107,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250897</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1188,6 +1213,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250911</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1319,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250920</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1390,6 +1425,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250932</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,6 +1531,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250975</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250985</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1693,6 +1743,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250994</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251006</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1900,6 +1960,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251036</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251056</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251211</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2207,6 +2282,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251145</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2312,6 +2392,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251185</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2419,6 +2504,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251168</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2526,6 +2616,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250875</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2633,6 +2728,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250883</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2740,6 +2840,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131250961</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2847,6 +2952,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251048</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2954,6 +3064,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251203</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3055,6 +3170,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251025</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3156,6 +3276,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251035</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3257,8 +3382,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131251201</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>